--- a/data/trans_dic/KIDMED_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,04; 73,07</t>
+          <t>58,7; 74,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,7; 71,59</t>
+          <t>58,79; 74,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,49; 70,28</t>
+          <t>60,89; 71,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,13; 68,24</t>
+          <t>53,9; 72,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,23; 70,87</t>
+          <t>52,98; 70,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,8; 67,43</t>
+          <t>56,21; 68,29</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,39; 79,42</t>
+          <t>59,92; 80,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,87; 78,47</t>
+          <t>54,71; 79,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,09; 75,61</t>
+          <t>62,38; 77,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,61; 61,31</t>
+          <t>56,59; 70,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,38; 69,98</t>
+          <t>50,89; 63,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,03; 63,34</t>
+          <t>56,06; 65,53</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>61,71%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,64; 70,1</t>
+          <t>46,07; 67,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,92; 66,63</t>
+          <t>57,16; 71,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,06; 66,25</t>
+          <t>54,45; 67,39</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60,36; 78,13</t>
+          <t>53,72; 75,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,36; 73,89</t>
+          <t>58,99; 77,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,53; 73,62</t>
+          <t>59,82; 73,96</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,03; 64,6</t>
+          <t>60,28; 67,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58,49; 66,39</t>
+          <t>59,88; 66,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,08; 64,24</t>
+          <t>61,11; 66,41</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>102</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65887</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85934</t>
+          <t>66868</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151821</t>
+          <t>147193</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55979; 74315</t>
+          <t>71148; 89732</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72586; 96767</t>
+          <t>58992; 74495</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136183; 166487</t>
+          <t>134901; 159375</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58988</t>
+          <t>58357</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>115738</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48689; 63728</t>
+          <t>48447; 64952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49877; 66409</t>
+          <t>50548; 66929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102523; 126168</t>
+          <t>104150; 126535</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42459</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>75977</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28746; 39782</t>
+          <t>33461; 44941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34200; 48916</t>
+          <t>28456; 41548</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67558; 85005</t>
+          <t>67281; 83939</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>161</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>110399</t>
+          <t>126178</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>134865</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245265</t>
+          <t>227838</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74595; 132143</t>
+          <t>111666; 139388</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>119892; 148817</t>
+          <t>89884; 111886</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192805; 271239</t>
+          <t>209656; 245049</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>112</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72398</t>
+          <t>86053</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165404</t>
+          <t>161101</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61956; 80976</t>
+          <t>67077; 98338</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70040; 106250</t>
+          <t>66000; 82798</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140394; 182168</t>
+          <t>142154; 175924</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>47884</t>
+          <t>42709</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>49063</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91822</t>
+          <t>91773</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41584; 53830</t>
+          <t>35383; 49434</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36146; 51009</t>
+          <t>41500; 54801</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82104; 101534</t>
+          <t>81492; 100748</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>575</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>387562</t>
+          <t>432530</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>459189</t>
+          <t>387090</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>846751</t>
+          <t>819620</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>329203; 416766</t>
+          <t>407333; 456088</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>428358; 486251</t>
+          <t>365390; 405376</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>786273; 884898</t>
+          <t>785890; 853967</t>
         </is>
       </c>
     </row>
